--- a/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria</t>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 52,05</t>
+          <t>10,4; 48,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,66</t>
+          <t>0,0; 39,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,21</t>
+          <t>0,0; 67,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 43,17</t>
+          <t>4,96; 37,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,65; 46,91</t>
+          <t>8,59; 45,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,83</t>
+          <t>0,0; 39,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 35,79</t>
+          <t>10,57; 37,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 35,23</t>
+          <t>10,8; 38,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,85</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,81</t>
+          <t>0,0; 46,37</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 72,89</t>
+          <t>15,7; 71,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 55,03</t>
+          <t>19,65; 52,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,43</t>
+          <t>0,0; 71,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 38,14</t>
+          <t>4,57; 37,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 39,08</t>
+          <t>6,73; 34,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 42,23</t>
+          <t>5,48; 44,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 41,51</t>
+          <t>13,73; 43,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 39,0</t>
+          <t>16,51; 38,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 26,5</t>
+          <t>2,99; 24,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 36,76</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 73,58</t>
+          <t>11,08; 73,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,77; 70,22</t>
+          <t>16,49; 69,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,34</t>
+          <t>0,0; 48,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,51</t>
+          <t>0,0; 44,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 51,88</t>
+          <t>19,28; 52,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,89</t>
+          <t>0,0; 33,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 47,38</t>
+          <t>12,77; 48,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,34; 52,77</t>
+          <t>23,56; 52,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,06</t>
+          <t>0,0; 24,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,44</t>
+          <t>0,0; 28,97</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,64</t>
+          <t>0,0; 44,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,33; 82,23</t>
+          <t>40,21; 87,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,84</t>
+          <t>0,0; 39,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 44,3</t>
+          <t>9,57; 43,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 50,5</t>
+          <t>6,32; 50,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,81</t>
+          <t>0,0; 50,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 28,35</t>
+          <t>3,01; 30,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 56,85</t>
+          <t>26,28; 55,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 50,67</t>
+          <t>9,24; 45,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,65</t>
+          <t>0,0; 30,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,2; 40,43</t>
+          <t>16,7; 40,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,63; 52,6</t>
+          <t>29,18; 51,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,92</t>
+          <t>3,8; 35,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,43</t>
+          <t>8,31; 26,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,51</t>
+          <t>17,87; 34,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 26,39</t>
+          <t>8,11; 28,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 28,35</t>
+          <t>14,11; 29,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,15</t>
+          <t>25,25; 38,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,41</t>
+          <t>5,7; 18,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 16,92</t>
+          <t>1,9; 17,67</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1341; 6273</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3608</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2369</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>657; 5029</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1406; 7446</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3902</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2761; 9736</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2749; 9742</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4162</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2692</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7752</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11119</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1106; 5036</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4211; 11286</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3236</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>626; 5090</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1312; 6719</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>607; 4889</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2849; 8966</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6758; 15724</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>599; 4960</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3834</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>702; 4682</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1401; 5916</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3172</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3963</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3498; 9586</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2647</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1945; 7413</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6277; 13978</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3052</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4298</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12986</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3988</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5110; 11158</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2954</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4200</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1854; 8508</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>743; 5941</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3843</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>594; 6038</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8430; 17884</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1360; 6658</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3037</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20980</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39538</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5896; 14142</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15090; 26797</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3583</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>652; 6040</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3867; 12335</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13112; 25075</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11436</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3557</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11547; 23800</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>31581; 48464</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3650; 11910</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>781; 7278</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 48,67</t>
+          <t>10,13; 48,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,76</t>
+          <t>0,0; 39,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,75</t>
+          <t>0,0; 66,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 37,97</t>
+          <t>4,98; 37,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 45,48</t>
+          <t>11,74; 47,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,1</t>
+          <t>0,0; 39,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 37,26</t>
+          <t>10,29; 36,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 38,29</t>
+          <t>10,35; 37,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 31,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,37</t>
+          <t>0,0; 47,54</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 71,48</t>
+          <t>14,8; 73,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 52,66</t>
+          <t>20,36; 53,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,22 +872,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,41</t>
+          <t>0,0; 83,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 37,14</t>
+          <t>4,85; 41,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 34,47</t>
+          <t>6,86; 37,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 44,12</t>
+          <t>5,51; 42,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,73; 43,22</t>
+          <t>12,98; 43,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 38,42</t>
+          <t>16,39; 38,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 24,75</t>
+          <t>2,97; 26,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,76</t>
+          <t>0,0; 36,7</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 73,95</t>
+          <t>10,87; 72,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 69,61</t>
+          <t>15,13; 68,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,22 +1012,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,45</t>
+          <t>0,0; 46,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,56</t>
+          <t>0,0; 47,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,28; 52,84</t>
+          <t>18,9; 54,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,54</t>
+          <t>0,0; 38,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 48,68</t>
+          <t>9,21; 48,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,56; 52,47</t>
+          <t>23,62; 52,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,7</t>
+          <t>0,0; 22,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,97</t>
+          <t>0,0; 25,16</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,11</t>
+          <t>0,0; 35,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,21; 87,8</t>
+          <t>39,97; 87,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,3</t>
+          <t>0,0; 39,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 43,92</t>
+          <t>10,79; 43,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 50,48</t>
+          <t>6,04; 48,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,98</t>
+          <t>0,0; 42,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 30,61</t>
+          <t>2,91; 27,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 55,75</t>
+          <t>26,76; 56,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 45,22</t>
+          <t>9,79; 48,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,03</t>
+          <t>0,0; 29,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,7; 40,06</t>
+          <t>16,38; 41,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,18; 51,82</t>
+          <t>29,94; 53,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 35,21</t>
+          <t>3,94; 33,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,31; 26,51</t>
+          <t>8,76; 26,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,17</t>
+          <t>18,1; 34,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,08</t>
+          <t>7,52; 26,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 29,08</t>
+          <t>14,35; 28,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,25; 38,74</t>
+          <t>25,15; 38,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,58</t>
+          <t>5,82; 18,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,67</t>
+          <t>2,01; 15,96</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1341; 6273</t>
+          <t>1305; 6198</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3567</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2369</t>
+          <t>0; 2340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>657; 5029</t>
+          <t>659; 4994</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1406; 7446</t>
+          <t>1922; 7704</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>0; 3954</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2761; 9736</t>
+          <t>2690; 9662</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2749; 9742</t>
+          <t>2633; 9469</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 5429</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2692</t>
+          <t>0; 2760</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1106; 5036</t>
+          <t>1043; 5148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4211; 11286</t>
+          <t>4364; 11422</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,22 +1868,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3236</t>
+          <t>0; 3778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>626; 5090</t>
+          <t>664; 5697</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1312; 6719</t>
+          <t>1337; 7372</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>607; 4889</t>
+          <t>610; 4702</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2849; 8966</t>
+          <t>2694; 8960</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6758; 15724</t>
+          <t>6706; 15696</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>599; 4960</t>
+          <t>595; 5213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 3829</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>702; 4682</t>
+          <t>688; 4584</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1401; 5916</t>
+          <t>1286; 5828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,22 +2076,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3172</t>
+          <t>0; 3070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3963</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3498; 9586</t>
+          <t>3429; 9812</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2647</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1945; 7413</t>
+          <t>1403; 7460</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6277; 13978</t>
+          <t>6291; 13948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 2791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>0; 3733</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5110; 11158</t>
+          <t>5079; 11144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2289,42 +2289,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1854; 8508</t>
+          <t>2091; 8420</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>743; 5941</t>
+          <t>710; 5743</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3843</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>594; 6038</t>
+          <t>575; 5352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8430; 17884</t>
+          <t>8583; 18026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1360; 6658</t>
+          <t>1441; 7171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3037</t>
+          <t>0; 3012</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5896; 14142</t>
+          <t>5782; 14713</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15090; 26797</t>
+          <t>15485; 27624</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>652; 6040</t>
+          <t>676; 5804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3867; 12335</t>
+          <t>4075; 12342</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13112; 25075</t>
+          <t>13283; 24956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3301; 11436</t>
+          <t>3063; 10637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11547; 23800</t>
+          <t>11747; 23448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31581; 48464</t>
+          <t>31462; 48005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3650; 11910</t>
+          <t>3729; 11888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>781; 7278</t>
+          <t>829; 6574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>26,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15,59%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 48,09</t>
+          <t>4,98; 43,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,32</t>
+          <t>11,65; 46,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 32,83</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 66,91</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 37,71</t>
+          <t>9,92; 52,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 47,06</t>
+          <t>0,0; 46,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 74,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 36,98</t>
+          <t>10,28; 35,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 37,22</t>
+          <t>10,57; 35,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,98</t>
+          <t>0,0; 20,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,54</t>
+          <t>0,0; 57,29</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 73,08</t>
+          <t>4,63; 38,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 53,3</t>
+          <t>6,68; 39,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>5,47; 42,23</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 83,35</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 41,57</t>
+          <t>14,92; 72,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 37,81</t>
+          <t>20,72; 55,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 42,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 74,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 43,19</t>
+          <t>13,43; 41,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 38,35</t>
+          <t>17,48; 39,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 26,02</t>
+          <t>3,03; 26,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,7</t>
+          <t>0,0; 34,29</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>42,64%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>43,42%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 72,4</t>
+          <t>0,0; 45,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 68,59</t>
+          <t>17,67; 51,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 33,89</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 46,9</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,86</t>
+          <t>11,01; 73,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 54,09</t>
+          <t>15,77; 70,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 48,99</t>
+          <t>9,67; 47,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,62; 52,36</t>
+          <t>22,34; 52,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,59</t>
+          <t>0,0; 21,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,16</t>
+          <t>0,0; 27,51</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24,99%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,26</t>
+          <t>0,0; 38,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,97; 87,69</t>
+          <t>11,06; 44,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>6,38; 50,5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 41,98</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 44,64</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,33; 82,23</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 39,36</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,79; 43,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,04; 48,8</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 42,63</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 27,14</t>
+          <t>2,91; 28,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,76; 56,19</t>
+          <t>27,38; 56,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 48,71</t>
+          <t>9,67; 50,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,78</t>
+          <t>0,0; 31,82</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>40,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,38; 41,67</t>
+          <t>8,76; 25,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,94; 53,42</t>
+          <t>17,87; 34,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>7,45; 26,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,84</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,53</t>
+          <t>17,2; 40,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 34,01</t>
+          <t>29,63; 52,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,12</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>4,12; 33,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,35; 28,66</t>
+          <t>14,38; 28,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,38</t>
+          <t>25,12; 38,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,55</t>
+          <t>6,19; 19,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,96</t>
+          <t>2,28; 17,29</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3397</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1414</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4138</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5540</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>756</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1305; 6198</t>
+          <t>659; 5717</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>1908; 7679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 3277</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2340</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>659; 4994</t>
+          <t>1278; 6708</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1922; 7704</t>
+          <t>0; 4234</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2722</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2690; 9662</t>
+          <t>2686; 9351</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2633; 9469</t>
+          <t>2690; 8964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5429</t>
+          <t>0; 3539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2760</t>
+          <t>0; 3356</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2847</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7752</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2514</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11119</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1962</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5360</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11119</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>860</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1043; 5148</t>
+          <t>635; 5227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4364; 11422</t>
+          <t>1303; 7619</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>606; 4680</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3778</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>664; 5697</t>
+          <t>1051; 5135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1337; 7372</t>
+          <t>4441; 11794</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>610; 4702</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3437</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2694; 8960</t>
+          <t>2786; 8613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6706; 15696</t>
+          <t>7153; 15963</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>595; 5213</t>
+          <t>606; 5310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3829</t>
+          <t>0; 3569</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3690</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6190</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9880</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>688; 4584</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1286; 5828</t>
+          <t>3206; 9412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 2674</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3070</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>697; 4659</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3429; 9812</t>
+          <t>1341; 5967</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3054</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3231</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1403; 7460</t>
+          <t>1472; 7214</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6291; 13948</t>
+          <t>5951; 14058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3733</t>
+          <t>0; 3810</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,44 +2201,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8124</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4862</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2185</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>646</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>0; 4150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5079; 11144</t>
+          <t>2142; 8581</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>751; 5943</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2832</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4035</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4998; 10450</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0; 2954</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4205</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2091; 8420</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>710; 5743</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3213</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>575; 5352</t>
+          <t>574; 5591</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8583; 18026</t>
+          <t>8783; 18237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1441; 7171</t>
+          <t>1424; 7460</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>0; 2965</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9737</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>20980</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2291</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18558</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2996</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5782; 14713</t>
+          <t>4075; 11831</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15485; 27624</t>
+          <t>13114; 25322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>3033; 10746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>676; 5804</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4075; 12342</t>
+          <t>6071; 14275</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13283; 24956</t>
+          <t>15323; 27200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3063; 10637</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>707; 5701</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11747; 23448</t>
+          <t>11767; 23199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31462; 48005</t>
+          <t>31420; 47721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3729; 11888</t>
+          <t>3964; 12439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>829; 6574</t>
+          <t>900; 6818</t>
         </is>
       </c>
     </row>
